--- a/DesignData/Excel_Masters/EnemyStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="76">
   <si>
     <t>AttackTypeTag</t>
   </si>
@@ -96,15 +93,169 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Zombie</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>Balrog</t>
+  </si>
+  <si>
+    <t>Bearking</t>
+  </si>
+  <si>
+    <t>BombSpider</t>
+  </si>
+  <si>
+    <t>BronzeGear</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Cursedmass</t>
+  </si>
+  <si>
+    <t>DanceMakane</t>
+  </si>
+  <si>
+    <t>Deatheye</t>
+  </si>
+  <si>
+    <t>DieS</t>
+  </si>
+  <si>
+    <t>DoctorMacaron</t>
+  </si>
+  <si>
+    <t>Famine</t>
+  </si>
+  <si>
+    <t>FelicisMachine</t>
+  </si>
+  <si>
+    <t>FelicisShinobi</t>
+  </si>
+  <si>
+    <t>Fiti</t>
+  </si>
+  <si>
+    <t>Gemini_Scythe</t>
+  </si>
+  <si>
+    <t>GhostMacaron</t>
+  </si>
+  <si>
+    <t>Graf</t>
+  </si>
+  <si>
+    <t>GuardianTreant</t>
+  </si>
+  <si>
+    <t>HackingTool</t>
+  </si>
+  <si>
+    <t>Hanged_Macaron</t>
+  </si>
+  <si>
+    <t>HoneyMos</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Karakasa</t>
+  </si>
+  <si>
+    <t>Kraken</t>
+  </si>
+  <si>
+    <t>KrakenTentacle</t>
+  </si>
+  <si>
+    <t>Leechking</t>
+  </si>
+  <si>
+    <t>LikeStatue</t>
+  </si>
+  <si>
+    <t>LordFelice</t>
+  </si>
+  <si>
+    <t>Makane</t>
+  </si>
+  <si>
+    <t>Mandragora</t>
+  </si>
+  <si>
+    <t>MaskScarecrow</t>
+  </si>
+  <si>
+    <t>Mechanicus</t>
+  </si>
+  <si>
+    <t>Megaron</t>
+  </si>
+  <si>
+    <t>Mimic</t>
+  </si>
+  <si>
+    <t>Octopus</t>
+  </si>
+  <si>
+    <t>PistolShrimp</t>
+  </si>
+  <si>
+    <t>Pufferfish</t>
+  </si>
+  <si>
+    <t>Seasoner</t>
+  </si>
+  <si>
+    <t>SharkRider</t>
+  </si>
+  <si>
+    <t>SoundPro</t>
+  </si>
+  <si>
+    <t>Starspawn</t>
+  </si>
+  <si>
+    <t>TinWoodman</t>
+  </si>
+  <si>
+    <t>Ushabti</t>
+  </si>
+  <si>
+    <t>Wagon</t>
+  </si>
+  <si>
+    <t>Watcher</t>
+  </si>
+  <si>
+    <t>Weaponmaster</t>
+  </si>
+  <si>
+    <t>Wolfron</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>AttackSpeed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>Unit.Rank.Boss</t>
+  </si>
+  <si>
+    <t>Unit.Attack.Range</t>
+  </si>
+  <si>
+    <t>Unit.Role.Tanker</t>
+  </si>
+  <si>
+    <t>Unit.Role.Support</t>
+  </si>
+  <si>
+    <t>Unit.Rank.Elite</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.625" customWidth="1"/>
@@ -1033,43 +1184,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1077,39 +1228,1925 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E2">
+        <v>1.24</v>
+      </c>
+      <c r="F2">
+        <v>150</v>
+      </c>
+      <c r="G2">
+        <v>2.1</v>
+      </c>
+      <c r="H2">
+        <v>3200</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>40</v>
+      </c>
+      <c r="L2">
+        <v>600</v>
+      </c>
+      <c r="M2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3">
+        <v>1.24</v>
+      </c>
+      <c r="F3">
+        <v>750</v>
+      </c>
+      <c r="G3">
+        <v>1.5</v>
+      </c>
+      <c r="H3">
+        <v>2560</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>28</v>
+      </c>
+      <c r="L3">
+        <v>500</v>
+      </c>
+      <c r="M3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0.88</v>
+      </c>
+      <c r="F4">
+        <v>150</v>
+      </c>
+      <c r="G4">
+        <v>1.3</v>
+      </c>
+      <c r="H4">
+        <v>600</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <v>30</v>
+      </c>
+      <c r="L4">
+        <v>500</v>
+      </c>
+      <c r="M4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>0.85</v>
+      </c>
+      <c r="F5">
+        <v>600</v>
+      </c>
+      <c r="G5">
+        <v>1.3</v>
+      </c>
+      <c r="H5">
+        <v>288</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>14</v>
+      </c>
+      <c r="L5">
+        <v>400</v>
+      </c>
+      <c r="M5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>1.18</v>
+      </c>
+      <c r="F6">
+        <v>900</v>
+      </c>
+      <c r="G6">
+        <v>1.9</v>
+      </c>
+      <c r="H6">
+        <v>288</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>500</v>
+      </c>
+      <c r="M6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>0.87</v>
+      </c>
+      <c r="F7">
+        <v>600</v>
+      </c>
+      <c r="G7">
+        <v>1.3</v>
+      </c>
+      <c r="H7">
+        <v>320</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+      <c r="L7">
+        <v>450</v>
+      </c>
+      <c r="M7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>1.22</v>
+      </c>
+      <c r="F8">
+        <v>150</v>
+      </c>
+      <c r="G8">
+        <v>1.4</v>
+      </c>
+      <c r="H8">
+        <v>400</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>400</v>
+      </c>
+      <c r="M8">
         <v>0.1</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>0.9</v>
+      </c>
+      <c r="F9">
+        <v>900</v>
+      </c>
+      <c r="G9">
+        <v>1.2</v>
+      </c>
+      <c r="H9">
+        <v>320</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
+        <v>14</v>
+      </c>
+      <c r="L9">
+        <v>500</v>
+      </c>
+      <c r="M9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>1.28</v>
+      </c>
+      <c r="F10">
+        <v>150</v>
+      </c>
+      <c r="G10">
+        <v>2.1</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>24</v>
+      </c>
+      <c r="K10">
+        <v>30</v>
+      </c>
+      <c r="L10">
+        <v>600</v>
+      </c>
+      <c r="M10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11">
+        <v>1.28</v>
+      </c>
+      <c r="F11">
+        <v>600</v>
+      </c>
+      <c r="G11">
+        <v>2.1</v>
+      </c>
+      <c r="H11">
+        <v>288</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>28</v>
+      </c>
+      <c r="K11">
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <v>500</v>
+      </c>
+      <c r="M11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="F12">
+        <v>150</v>
+      </c>
+      <c r="G12">
+        <v>1.2</v>
+      </c>
+      <c r="H12">
+        <v>3200</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>40</v>
+      </c>
+      <c r="L12">
+        <v>400</v>
+      </c>
+      <c r="M12">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>150</v>
+      </c>
+      <c r="G13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H13">
+        <v>360</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <v>20</v>
+      </c>
+      <c r="L13">
+        <v>450</v>
+      </c>
+      <c r="M13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F14">
+        <v>750</v>
+      </c>
+      <c r="G14">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H14">
+        <v>320</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14">
+        <v>14</v>
+      </c>
+      <c r="L14">
+        <v>500</v>
+      </c>
+      <c r="M14">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F15">
+        <v>150</v>
+      </c>
+      <c r="G15">
+        <v>2.4</v>
+      </c>
+      <c r="H15">
+        <v>600</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>24</v>
+      </c>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
+        <v>450</v>
+      </c>
+      <c r="M15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F16">
+        <v>150</v>
+      </c>
+      <c r="G16">
+        <v>1.5</v>
+      </c>
+      <c r="H16">
+        <v>600</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>24</v>
+      </c>
+      <c r="K16">
+        <v>30</v>
+      </c>
+      <c r="L16">
+        <v>450</v>
+      </c>
+      <c r="M16">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>1.01</v>
+      </c>
+      <c r="F17">
+        <v>150</v>
+      </c>
+      <c r="G17">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H17">
+        <v>400</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>40</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>450</v>
+      </c>
+      <c r="M17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>1.07</v>
+      </c>
+      <c r="F18">
+        <v>150</v>
+      </c>
+      <c r="G18">
+        <v>1.3</v>
+      </c>
+      <c r="H18">
+        <v>400</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>40</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>550</v>
+      </c>
+      <c r="M18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F19">
+        <v>150</v>
+      </c>
+      <c r="G19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H19">
+        <v>3200</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>40</v>
+      </c>
+      <c r="L19">
+        <v>500</v>
+      </c>
+      <c r="M19">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20">
+        <v>0.91</v>
+      </c>
+      <c r="F20">
+        <v>900</v>
+      </c>
+      <c r="G20">
+        <v>1.2</v>
+      </c>
+      <c r="H20">
+        <v>640</v>
+      </c>
+      <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
+        <v>60</v>
+      </c>
+      <c r="K20">
+        <v>16.8</v>
+      </c>
+      <c r="L20">
+        <v>550</v>
+      </c>
+      <c r="M20">
         <v>0.2</v>
       </c>
-      <c r="H2">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F21">
+        <v>900</v>
+      </c>
+      <c r="G21">
+        <v>1.6</v>
+      </c>
+      <c r="H21">
+        <v>320</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>40</v>
+      </c>
+      <c r="K21">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>550</v>
+      </c>
+      <c r="M21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>0.92</v>
+      </c>
+      <c r="F22">
+        <v>150</v>
+      </c>
+      <c r="G22">
+        <v>1.2</v>
+      </c>
+      <c r="H22">
+        <v>400</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>40</v>
+      </c>
+      <c r="K22">
+        <v>20</v>
+      </c>
+      <c r="L22">
+        <v>450</v>
+      </c>
+      <c r="M22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="J2">
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <v>0.82</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>360</v>
+      </c>
+      <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
+        <v>28</v>
+      </c>
+      <c r="K23">
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <v>550</v>
+      </c>
+      <c r="M23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>0.93</v>
+      </c>
+      <c r="F24">
+        <v>900</v>
+      </c>
+      <c r="G24">
+        <v>1.4</v>
+      </c>
+      <c r="H24">
+        <v>480</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
+        <v>24</v>
+      </c>
+      <c r="K24">
+        <v>21</v>
+      </c>
+      <c r="L24">
+        <v>500</v>
+      </c>
+      <c r="M24">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="K2">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25">
+        <v>0.92</v>
+      </c>
+      <c r="F25">
+        <v>150</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3200</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>40</v>
+      </c>
+      <c r="L25">
+        <v>450</v>
+      </c>
+      <c r="M25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26">
+        <v>0.93</v>
+      </c>
+      <c r="F26">
+        <v>600</v>
+      </c>
+      <c r="G26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H26">
+        <v>576</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
+        <v>42</v>
+      </c>
+      <c r="K26">
+        <v>16.8</v>
+      </c>
+      <c r="L26">
+        <v>450</v>
+      </c>
+      <c r="M26">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="L2">
-        <v>1000</v>
-      </c>
-      <c r="M2">
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F27">
+        <v>150</v>
+      </c>
+      <c r="G27">
+        <v>2.1</v>
+      </c>
+      <c r="H27">
+        <v>3200</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>40</v>
+      </c>
+      <c r="L27">
+        <v>600</v>
+      </c>
+      <c r="M27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28">
+        <v>0.91</v>
+      </c>
+      <c r="F28">
+        <v>900</v>
+      </c>
+      <c r="G28">
+        <v>1.6</v>
+      </c>
+      <c r="H28">
+        <v>480</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
+        <v>24</v>
+      </c>
+      <c r="K28">
+        <v>21</v>
+      </c>
+      <c r="L28">
+        <v>400</v>
+      </c>
+      <c r="M28">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29">
+        <v>1.04</v>
+      </c>
+      <c r="F29">
+        <v>750</v>
+      </c>
+      <c r="G29">
+        <v>1.7</v>
+      </c>
+      <c r="H29">
+        <v>2560</v>
+      </c>
+      <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>28</v>
+      </c>
+      <c r="L29">
+        <v>600</v>
+      </c>
+      <c r="M29">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30">
+        <v>0.9</v>
+      </c>
+      <c r="F30">
+        <v>150</v>
+      </c>
+      <c r="G30">
+        <v>2.1</v>
+      </c>
+      <c r="H30">
+        <v>600</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>24</v>
+      </c>
+      <c r="K30">
+        <v>30</v>
+      </c>
+      <c r="L30">
+        <v>550</v>
+      </c>
+      <c r="M30">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31">
+        <v>1.24</v>
+      </c>
+      <c r="F31">
+        <v>750</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>960</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>36</v>
+      </c>
+      <c r="K31">
+        <v>25.2</v>
+      </c>
+      <c r="L31">
+        <v>550</v>
+      </c>
+      <c r="M31">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32">
+        <v>0.91</v>
+      </c>
+      <c r="F32">
+        <v>750</v>
+      </c>
+      <c r="G32">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H32">
+        <v>288</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>28</v>
+      </c>
+      <c r="K32">
+        <v>14</v>
+      </c>
+      <c r="L32">
+        <v>500</v>
+      </c>
+      <c r="M32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33">
+        <v>0.83</v>
+      </c>
+      <c r="F33">
+        <v>900</v>
+      </c>
+      <c r="G33">
+        <v>1.9</v>
+      </c>
+      <c r="H33">
+        <v>320</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>40</v>
+      </c>
+      <c r="K33">
+        <v>14</v>
+      </c>
+      <c r="L33">
+        <v>400</v>
+      </c>
+      <c r="M33">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34">
+        <v>1.06</v>
+      </c>
+      <c r="F34">
+        <v>750</v>
+      </c>
+      <c r="G34">
+        <v>2.4</v>
+      </c>
+      <c r="H34">
+        <v>2560</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>28</v>
+      </c>
+      <c r="L34">
+        <v>500</v>
+      </c>
+      <c r="M34">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F35">
+        <v>150</v>
+      </c>
+      <c r="G35">
+        <v>1.7</v>
+      </c>
+      <c r="H35">
+        <v>720</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>42</v>
+      </c>
+      <c r="K35">
+        <v>24</v>
+      </c>
+      <c r="L35">
+        <v>600</v>
+      </c>
+      <c r="M35">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36">
+        <v>1.2</v>
+      </c>
+      <c r="F36">
+        <v>600</v>
+      </c>
+      <c r="G36">
+        <v>1.8</v>
+      </c>
+      <c r="H36">
+        <v>320</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
+        <v>40</v>
+      </c>
+      <c r="K36">
+        <v>14</v>
+      </c>
+      <c r="L36">
+        <v>400</v>
+      </c>
+      <c r="M36">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F37">
+        <v>150</v>
+      </c>
+      <c r="G37">
+        <v>2.1</v>
+      </c>
+      <c r="H37">
+        <v>600</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>24</v>
+      </c>
+      <c r="K37">
+        <v>30</v>
+      </c>
+      <c r="L37">
+        <v>550</v>
+      </c>
+      <c r="M37">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38">
+        <v>0.87</v>
+      </c>
+      <c r="F38">
+        <v>750</v>
+      </c>
+      <c r="G38">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H38">
+        <v>320</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>40</v>
+      </c>
+      <c r="K38">
+        <v>14</v>
+      </c>
+      <c r="L38">
+        <v>450</v>
+      </c>
+      <c r="M38">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F39">
+        <v>750</v>
+      </c>
+      <c r="G39">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H39">
+        <v>288</v>
+      </c>
+      <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
+        <v>28</v>
+      </c>
+      <c r="K39">
+        <v>14</v>
+      </c>
+      <c r="L39">
+        <v>600</v>
+      </c>
+      <c r="M39">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>0.83</v>
+      </c>
+      <c r="F40">
+        <v>150</v>
+      </c>
+      <c r="G40">
+        <v>2.4</v>
+      </c>
+      <c r="H40">
+        <v>400</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>40</v>
+      </c>
+      <c r="K40">
+        <v>20</v>
+      </c>
+      <c r="L40">
+        <v>600</v>
+      </c>
+      <c r="M40">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F41">
+        <v>150</v>
+      </c>
+      <c r="G41">
+        <v>1.7</v>
+      </c>
+      <c r="H41">
+        <v>400</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>40</v>
+      </c>
+      <c r="K41">
+        <v>20</v>
+      </c>
+      <c r="L41">
+        <v>500</v>
+      </c>
+      <c r="M41">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42">
+        <v>1.01</v>
+      </c>
+      <c r="F42">
+        <v>150</v>
+      </c>
+      <c r="G42">
+        <v>2.1</v>
+      </c>
+      <c r="H42">
+        <v>800</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>60</v>
+      </c>
+      <c r="K42">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>550</v>
+      </c>
+      <c r="M42">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43">
+        <v>0.99</v>
+      </c>
+      <c r="F43">
+        <v>750</v>
+      </c>
+      <c r="G43">
+        <v>1.5</v>
+      </c>
+      <c r="H43">
+        <v>320</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>40</v>
+      </c>
+      <c r="K43">
+        <v>14</v>
+      </c>
+      <c r="L43">
+        <v>500</v>
+      </c>
+      <c r="M43">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44">
+        <v>1.23</v>
+      </c>
+      <c r="F44">
+        <v>750</v>
+      </c>
+      <c r="G44">
+        <v>2.1</v>
+      </c>
+      <c r="H44">
+        <v>960</v>
+      </c>
+      <c r="I44">
+        <v>100</v>
+      </c>
+      <c r="J44">
+        <v>36</v>
+      </c>
+      <c r="K44">
+        <v>25.2</v>
+      </c>
+      <c r="L44">
+        <v>450</v>
+      </c>
+      <c r="M44">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45">
+        <v>1.06</v>
+      </c>
+      <c r="F45">
+        <v>150</v>
+      </c>
+      <c r="G45">
+        <v>2.1</v>
+      </c>
+      <c r="H45">
+        <v>800</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>60</v>
+      </c>
+      <c r="K45">
+        <v>24</v>
+      </c>
+      <c r="L45">
+        <v>550</v>
+      </c>
+      <c r="M45">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46">
+        <v>1.05</v>
+      </c>
+      <c r="F46">
+        <v>150</v>
+      </c>
+      <c r="G46">
+        <v>1.9</v>
+      </c>
+      <c r="H46">
+        <v>400</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>40</v>
+      </c>
+      <c r="K46">
+        <v>20</v>
+      </c>
+      <c r="L46">
+        <v>550</v>
+      </c>
+      <c r="M46">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47">
+        <v>1.22</v>
+      </c>
+      <c r="F47">
+        <v>150</v>
+      </c>
+      <c r="G47">
+        <v>2.1</v>
+      </c>
+      <c r="H47">
+        <v>3200</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>100</v>
+      </c>
+      <c r="K47">
+        <v>40</v>
+      </c>
+      <c r="L47">
+        <v>500</v>
+      </c>
+      <c r="M47">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48">
+        <v>1.01</v>
+      </c>
+      <c r="F48">
+        <v>150</v>
+      </c>
+      <c r="G48">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H48">
+        <v>400</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>40</v>
+      </c>
+      <c r="K48">
+        <v>20</v>
+      </c>
+      <c r="L48">
+        <v>450</v>
+      </c>
+      <c r="M48">
         <v>0.1</v>
       </c>
     </row>
@@ -1143,6 +3180,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -1182,32 +3220,32 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyStats_Master.xlsx
@@ -5,22 +5,24 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24840" windowHeight="9645"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyStats_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Tags" sheetId="2" r:id="rId2"/>
+    <sheet name="EnemyStats" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="116">
+  <si>
+    <t>---</t>
+  </si>
   <si>
     <t>AttackTypeTag</t>
   </si>
@@ -31,7 +33,13 @@
     <t>RankTypeTag</t>
   </si>
   <si>
-    <t>AttackRange</t>
+    <t>BasicAttackActionID</t>
+  </si>
+  <si>
+    <t>SkillActionIDs</t>
+  </si>
+  <si>
+    <t>SummonCost</t>
   </si>
   <si>
     <t>BaseMaxHP</t>
@@ -52,62 +60,42 @@
     <t>BaseCritRate</t>
   </si>
   <si>
-    <t>Unit.Attack.Melee</t>
-  </si>
-  <si>
-    <t>Unit.Attack.Melee</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Attack.Range</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Tanker</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Support</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Normal</t>
-  </si>
-  <si>
-    <t>Unit.Rank.Normal</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Elite</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Boss</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
     <t>Balrog</t>
   </si>
   <si>
+    <t>(TagName="Unit.Attack.Melee")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Dealer")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Boss")</t>
+  </si>
+  <si>
+    <t>("M_Balrog_Skl1","M_Balrog_Skl2")</t>
+  </si>
+  <si>
     <t>Bearking</t>
   </si>
   <si>
+    <t>(TagName="Unit.Attack.Range")</t>
+  </si>
+  <si>
     <t>BombSpider</t>
   </si>
   <si>
+    <t>(TagName="Unit.Role.Tanker")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Normal")</t>
+  </si>
+  <si>
     <t>BronzeGear</t>
   </si>
   <si>
+    <t>(TagName="Unit.Role.Support")</t>
+  </si>
+  <si>
     <t>Cell</t>
   </si>
   <si>
@@ -117,9 +105,15 @@
     <t>DanceMakane</t>
   </si>
   <si>
+    <t>M_DanceMakane_Atk</t>
+  </si>
+  <si>
     <t>Deatheye</t>
   </si>
   <si>
+    <t>M_Deatheye_Atk</t>
+  </si>
+  <si>
     <t>DieS</t>
   </si>
   <si>
@@ -153,6 +147,9 @@
     <t>HackingTool</t>
   </si>
   <si>
+    <t>(TagName="Unit.Rank.Elite")</t>
+  </si>
+  <si>
     <t>Hanged_Macaron</t>
   </si>
   <si>
@@ -237,25 +234,139 @@
     <t>Wolfron</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
-    <t>Unit.Rank.Boss</t>
-  </si>
-  <si>
-    <t>Unit.Attack.Range</t>
-  </si>
-  <si>
-    <t>Unit.Role.Tanker</t>
-  </si>
-  <si>
-    <t>Unit.Role.Support</t>
-  </si>
-  <si>
-    <t>Unit.Rank.Elite</t>
+    <t>M_Balrog_Atk</t>
+  </si>
+  <si>
+    <t>M_Bearking_Atk</t>
+  </si>
+  <si>
+    <t>M_BombSpider_Atk</t>
+  </si>
+  <si>
+    <t>M_BronzeGear_Atk</t>
+  </si>
+  <si>
+    <t>M_Cell_Atk</t>
+  </si>
+  <si>
+    <t>M_Cursedmass_Atk</t>
+  </si>
+  <si>
+    <t>M_DieS_Atk</t>
+  </si>
+  <si>
+    <t>M_DoctorMacaron_Atk</t>
+  </si>
+  <si>
+    <t>M_Famine_Atk</t>
+  </si>
+  <si>
+    <t>M_FelicisMachine_Atk</t>
+  </si>
+  <si>
+    <t>M_FelicisShinobi_Atk</t>
+  </si>
+  <si>
+    <t>M_Fiti_Atk</t>
+  </si>
+  <si>
+    <t>M_Gemini_Scythe_Atk</t>
+  </si>
+  <si>
+    <t>M_GhostMacaron_Atk</t>
+  </si>
+  <si>
+    <t>M_Graf_Atk</t>
+  </si>
+  <si>
+    <t>M_GuardianTreant_Atk</t>
+  </si>
+  <si>
+    <t>M_HackingTool_Atk</t>
+  </si>
+  <si>
+    <t>M_Hanged_Macaron_Atk</t>
+  </si>
+  <si>
+    <t>M_HoneyMos_Atk</t>
+  </si>
+  <si>
+    <t>M_Jellyfish_Atk</t>
+  </si>
+  <si>
+    <t>M_Karakasa_Atk</t>
+  </si>
+  <si>
+    <t>M_Kraken_Atk</t>
+  </si>
+  <si>
+    <t>M_KrakenTentacle_Atk</t>
+  </si>
+  <si>
+    <t>M_Leechking_Atk</t>
+  </si>
+  <si>
+    <t>M_LikeStatue_Atk</t>
+  </si>
+  <si>
+    <t>M_LordFelice_Atk</t>
+  </si>
+  <si>
+    <t>M_Makane_Atk</t>
+  </si>
+  <si>
+    <t>M_Mandragora_Atk</t>
+  </si>
+  <si>
+    <t>M_MaskScarecrow_Atk</t>
+  </si>
+  <si>
+    <t>M_Mechanicus_Atk</t>
+  </si>
+  <si>
+    <t>M_Megaron_Atk</t>
+  </si>
+  <si>
+    <t>M_Mimic_Atk</t>
+  </si>
+  <si>
+    <t>M_Octopus_Atk</t>
+  </si>
+  <si>
+    <t>M_PistolShrimp_Atk</t>
+  </si>
+  <si>
+    <t>M_Pufferfish_Atk</t>
+  </si>
+  <si>
+    <t>M_Seasoner_Atk</t>
+  </si>
+  <si>
+    <t>M_SharkRider_Atk</t>
+  </si>
+  <si>
+    <t>M_SoundPro_Atk</t>
+  </si>
+  <si>
+    <t>M_Starspawn_Atk</t>
+  </si>
+  <si>
+    <t>M_TinWoodman_Atk</t>
+  </si>
+  <si>
+    <t>M_Ushabti_Atk</t>
+  </si>
+  <si>
+    <t>M_Wagon_Atk</t>
+  </si>
+  <si>
+    <t>M_Watcher_Atk</t>
+  </si>
+  <si>
+    <t>M_Weaponmaster_Atk</t>
+  </si>
+  <si>
+    <t>M_Wolfron_Atk</t>
   </si>
 </sst>
 </file>
@@ -1176,74 +1287,71 @@
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="9.125" customWidth="1"/>
+    <col min="5" max="5" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>71</v>
       </c>
-      <c r="E2">
-        <v>1.24</v>
-      </c>
-      <c r="F2">
-        <v>150</v>
+      <c r="F2" t="s">
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>3200</v>
@@ -1266,25 +1374,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3">
-        <v>1.24</v>
-      </c>
-      <c r="F3">
-        <v>750</v>
-      </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>2560</v>
@@ -1307,25 +1412,22 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>0.88</v>
-      </c>
-      <c r="F4">
-        <v>150</v>
-      </c>
       <c r="G4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>600</v>
@@ -1348,25 +1450,22 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>74</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>0.85</v>
-      </c>
-      <c r="F5">
-        <v>600</v>
-      </c>
       <c r="G5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>288</v>
@@ -1389,25 +1488,22 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>1.18</v>
-      </c>
-      <c r="F6">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
       </c>
       <c r="G6">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>288</v>
@@ -1430,25 +1526,22 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>0.87</v>
-      </c>
-      <c r="F7">
-        <v>600</v>
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
       </c>
       <c r="G7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>320</v>
@@ -1471,25 +1564,22 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>1.22</v>
-      </c>
-      <c r="F8">
-        <v>150</v>
-      </c>
       <c r="G8">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>400</v>
@@ -1515,22 +1605,19 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9">
-        <v>0.9</v>
-      </c>
-      <c r="F9">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>320</v>
@@ -1553,25 +1640,22 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10">
-        <v>1.28</v>
-      </c>
-      <c r="F10">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
       </c>
       <c r="G10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>600</v>
@@ -1594,25 +1678,22 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>1.28</v>
-      </c>
-      <c r="F11">
-        <v>600</v>
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>78</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>288</v>
@@ -1635,25 +1716,22 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="F12">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
       </c>
       <c r="G12">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>3200</v>
@@ -1676,25 +1754,22 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>360</v>
@@ -1717,25 +1792,22 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F14">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
       </c>
       <c r="G14">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>320</v>
@@ -1758,25 +1830,22 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="F15">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
       </c>
       <c r="G15">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>600</v>
@@ -1799,25 +1868,22 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F16">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>83</v>
       </c>
       <c r="G16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>600</v>
@@ -1840,25 +1906,22 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17">
-        <v>1.01</v>
-      </c>
-      <c r="F17">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>84</v>
       </c>
       <c r="G17">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>400</v>
@@ -1881,25 +1944,22 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18">
-        <v>1.07</v>
-      </c>
-      <c r="F18">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
       </c>
       <c r="G18">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>400</v>
@@ -1922,25 +1982,22 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F19">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
       </c>
       <c r="G19">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>3200</v>
@@ -1963,25 +2020,22 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20">
-        <v>0.91</v>
-      </c>
-      <c r="F20">
-        <v>900</v>
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>87</v>
       </c>
       <c r="G20">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>640</v>
@@ -1993,7 +2047,7 @@
         <v>60</v>
       </c>
       <c r="K20">
-        <v>16.8</v>
+        <v>16.799999</v>
       </c>
       <c r="L20">
         <v>550</v>
@@ -2004,25 +2058,22 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F21">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>320</v>
@@ -2045,25 +2096,22 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22">
-        <v>0.92</v>
-      </c>
-      <c r="F22">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
+        <v>89</v>
       </c>
       <c r="G22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>400</v>
@@ -2086,25 +2134,22 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23">
-        <v>0.82</v>
-      </c>
-      <c r="F23">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>360</v>
@@ -2127,25 +2172,22 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24">
-        <v>0.93</v>
-      </c>
-      <c r="F24">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
       </c>
       <c r="G24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>480</v>
@@ -2168,25 +2210,22 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25">
-        <v>0.92</v>
-      </c>
-      <c r="F25">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>3200</v>
@@ -2209,25 +2248,22 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26">
-        <v>0.93</v>
-      </c>
-      <c r="F26">
-        <v>600</v>
+        <v>42</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
       </c>
       <c r="G26">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>576</v>
@@ -2239,7 +2275,7 @@
         <v>42</v>
       </c>
       <c r="K26">
-        <v>16.8</v>
+        <v>16.799999</v>
       </c>
       <c r="L26">
         <v>450</v>
@@ -2250,25 +2286,22 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F27">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
       </c>
       <c r="G27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>3200</v>
@@ -2291,25 +2324,22 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28">
-        <v>0.91</v>
-      </c>
-      <c r="F28">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>95</v>
       </c>
       <c r="G28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>480</v>
@@ -2332,25 +2362,22 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29">
-        <v>1.04</v>
-      </c>
-      <c r="F29">
-        <v>750</v>
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>96</v>
       </c>
       <c r="G29">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>2560</v>
@@ -2373,25 +2400,22 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30">
-        <v>0.9</v>
-      </c>
-      <c r="F30">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
+        <v>97</v>
       </c>
       <c r="G30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>600</v>
@@ -2414,25 +2438,22 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31">
-        <v>1.24</v>
-      </c>
-      <c r="F31">
-        <v>750</v>
+        <v>42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>960</v>
@@ -2444,7 +2465,7 @@
         <v>36</v>
       </c>
       <c r="K31">
-        <v>25.2</v>
+        <v>25.200001</v>
       </c>
       <c r="L31">
         <v>550</v>
@@ -2455,25 +2476,22 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32">
-        <v>0.91</v>
-      </c>
-      <c r="F32">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>99</v>
       </c>
       <c r="G32">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>288</v>
@@ -2496,25 +2514,22 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33">
-        <v>0.83</v>
-      </c>
-      <c r="F33">
-        <v>900</v>
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
+        <v>100</v>
       </c>
       <c r="G33">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>320</v>
@@ -2537,25 +2552,22 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34">
-        <v>1.06</v>
-      </c>
-      <c r="F34">
-        <v>750</v>
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>101</v>
       </c>
       <c r="G34">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>2560</v>
@@ -2578,25 +2590,22 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F35">
-        <v>150</v>
+        <v>42</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
       </c>
       <c r="G35">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>720</v>
@@ -2619,25 +2628,22 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36">
-        <v>1.2</v>
-      </c>
-      <c r="F36">
-        <v>600</v>
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>103</v>
       </c>
       <c r="G36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>320</v>
@@ -2660,25 +2666,22 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F37">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
+        <v>104</v>
       </c>
       <c r="G37">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>600</v>
@@ -2701,25 +2704,22 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38">
-        <v>0.87</v>
-      </c>
-      <c r="F38">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
       </c>
       <c r="G38">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>320</v>
@@ -2742,25 +2742,22 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F39">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
+        <v>106</v>
       </c>
       <c r="G39">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>288</v>
@@ -2783,25 +2780,22 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40">
-        <v>0.83</v>
-      </c>
-      <c r="F40">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E40" t="s">
+        <v>107</v>
       </c>
       <c r="G40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>400</v>
@@ -2824,25 +2818,22 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F41">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E41" t="s">
+        <v>108</v>
       </c>
       <c r="G41">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>400</v>
@@ -2865,25 +2856,22 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42">
-        <v>1.01</v>
-      </c>
-      <c r="F42">
-        <v>150</v>
+        <v>42</v>
+      </c>
+      <c r="E42" t="s">
+        <v>109</v>
       </c>
       <c r="G42">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>800</v>
@@ -2906,25 +2894,22 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43">
-        <v>0.99</v>
-      </c>
-      <c r="F43">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
+        <v>110</v>
       </c>
       <c r="G43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>320</v>
@@ -2947,25 +2932,22 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44">
-        <v>1.23</v>
-      </c>
-      <c r="F44">
-        <v>750</v>
+        <v>42</v>
+      </c>
+      <c r="E44" t="s">
+        <v>111</v>
       </c>
       <c r="G44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>960</v>
@@ -2977,7 +2959,7 @@
         <v>36</v>
       </c>
       <c r="K44">
-        <v>25.2</v>
+        <v>25.200001</v>
       </c>
       <c r="L44">
         <v>450</v>
@@ -2988,25 +2970,22 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45">
-        <v>1.06</v>
-      </c>
-      <c r="F45">
-        <v>150</v>
+        <v>42</v>
+      </c>
+      <c r="E45" t="s">
+        <v>112</v>
       </c>
       <c r="G45">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>800</v>
@@ -3029,25 +3008,22 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46">
-        <v>1.05</v>
-      </c>
-      <c r="F46">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>113</v>
       </c>
       <c r="G46">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>400</v>
@@ -3070,25 +3046,22 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47">
-        <v>1.22</v>
-      </c>
-      <c r="F47">
-        <v>150</v>
+        <v>16</v>
+      </c>
+      <c r="E47" t="s">
+        <v>114</v>
       </c>
       <c r="G47">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>3200</v>
@@ -3111,25 +3084,22 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48">
-        <v>1.01</v>
-      </c>
-      <c r="F48">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="E48" t="s">
+        <v>115</v>
       </c>
       <c r="G48">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>400</v>
@@ -3148,104 +3118,6 @@
       </c>
       <c r="M48">
         <v>0.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="8">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)" sqref="A1:A1048576">
-      <formula1>COUNTIF($A:$A, A1) &lt;= 1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)와 0은 입력할 수 없습니다. 0 보다 큰 숫자를 입력해주세요." sqref="E2:E1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류(Range)" error="공격 사거리는 0보다 작을 수 없습니다._x000a_(예: 100 = 1미터)" sqref="F1:F1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류 (Speed)" error="속도는 0보다 작을 수 없습니다._x000a_언리얼 단위(cm/s)입니다._x000a_(예: 100 = 1미터, 600 = 달리기 속도)" sqref="L1:L1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="최소 체력 오류" error="최대 체력(MaxHP)은 최소 1 이상이어야 합니다._x000a_0을 입력하면 유닛이 생성되자마자 죽습니다!" sqref="H1:H1048576">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="스탯 입력 오류" error="기본 스탯은 음수(-)일 수 없습니다._x000a_0 이상의 값을 입력해주세요." sqref="I1:K1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="확률 범위 오류 (0~1)" error="확률은 0.0 ~ 1.0 사이의 값만 가능합니다._x000a__x000a_[올바른 예시]_x000a_- 10% -&gt; 0.1 입력_x000a_- 50% -&gt; 0.5 입력_x000a_- 100% -&gt; 1.0 입력" sqref="M1:M1048576">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G2:G1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$C$1:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyStats_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24840" windowHeight="9645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyStats" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
   <si>
     <t>---</t>
   </si>
@@ -33,10 +33,10 @@
     <t>RankTypeTag</t>
   </si>
   <si>
-    <t>BasicAttackActionID</t>
-  </si>
-  <si>
-    <t>SkillActionIDs</t>
+    <t>BasicAttackActionHandle</t>
+  </si>
+  <si>
+    <t>PatternActionHandles</t>
   </si>
   <si>
     <t>SummonCost</t>
@@ -72,7 +72,10 @@
     <t>(TagName="Unit.Rank.Boss")</t>
   </si>
   <si>
-    <t>("M_Balrog_Skl1","M_Balrog_Skl2")</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Balrog")</t>
+  </si>
+  <si>
+    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Balrog_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Balrog_Pat2"))</t>
   </si>
   <si>
     <t>Bearking</t>
@@ -81,292 +84,244 @@
     <t>(TagName="Unit.Attack.Range")</t>
   </si>
   <si>
-    <t>BombSpider</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Bearking")</t>
+  </si>
+  <si>
+    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat2"))</t>
+  </si>
+  <si>
+    <t>BronzeGear</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Support")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Normal")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="BronzeGear")</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cell")</t>
+  </si>
+  <si>
+    <t>Cursedmass</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cursedmass")</t>
+  </si>
+  <si>
+    <t>DanceMakane</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="DanceMakane")</t>
+  </si>
+  <si>
+    <t>Deatheye</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Deatheye")</t>
+  </si>
+  <si>
+    <t>DieS</t>
   </si>
   <si>
     <t>(TagName="Unit.Role.Tanker")</t>
   </si>
   <si>
-    <t>(TagName="Unit.Rank.Normal")</t>
-  </si>
-  <si>
-    <t>BronzeGear</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Role.Support")</t>
-  </si>
-  <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>Cursedmass</t>
-  </si>
-  <si>
-    <t>DanceMakane</t>
-  </si>
-  <si>
-    <t>M_DanceMakane_Atk</t>
-  </si>
-  <si>
-    <t>Deatheye</t>
-  </si>
-  <si>
-    <t>M_Deatheye_Atk</t>
-  </si>
-  <si>
-    <t>DieS</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="DieS")</t>
   </si>
   <si>
     <t>DoctorMacaron</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="DoctorMacaron")</t>
+  </si>
+  <si>
     <t>Famine</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Famine")</t>
+  </si>
+  <si>
     <t>FelicisMachine</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="FelicisMachine")</t>
+  </si>
+  <si>
     <t>FelicisShinobi</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="FelicisShinobi")</t>
+  </si>
+  <si>
     <t>Fiti</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Fiti")</t>
+  </si>
+  <si>
     <t>Gemini_Scythe</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Gemini_Scythe")</t>
+  </si>
+  <si>
     <t>GhostMacaron</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="GhostMacaron")</t>
+  </si>
+  <si>
     <t>Graf</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Graf")</t>
+  </si>
+  <si>
     <t>GuardianTreant</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="GuardianTreant")</t>
+  </si>
+  <si>
+    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="GuardianTreant_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="GuardianTreant_Pat2"))</t>
+  </si>
+  <si>
     <t>HackingTool</t>
   </si>
   <si>
     <t>(TagName="Unit.Rank.Elite")</t>
   </si>
   <si>
-    <t>Hanged_Macaron</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="HackingTool")</t>
   </si>
   <si>
     <t>HoneyMos</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="HoneyMos")</t>
+  </si>
+  <si>
     <t>Jellyfish</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Jellyfish")</t>
+  </si>
+  <si>
     <t>Karakasa</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Karakasa")</t>
+  </si>
+  <si>
     <t>Kraken</t>
   </si>
   <si>
-    <t>KrakenTentacle</t>
-  </si>
-  <si>
-    <t>Leechking</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Kraken")</t>
   </si>
   <si>
     <t>LikeStatue</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="LikeStatue")</t>
+  </si>
+  <si>
     <t>LordFelice</t>
   </si>
   <si>
-    <t>Makane</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="LordFelice")</t>
   </si>
   <si>
     <t>Mandragora</t>
   </si>
   <si>
-    <t>MaskScarecrow</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Mandragora")</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Mask")</t>
   </si>
   <si>
     <t>Mechanicus</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Mechanicus")</t>
+  </si>
+  <si>
     <t>Megaron</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Megaron")</t>
+  </si>
+  <si>
+    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Megaron_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Megaron_Pat2"))</t>
+  </si>
+  <si>
     <t>Mimic</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Mimic")</t>
+  </si>
+  <si>
     <t>Octopus</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Octopus")</t>
+  </si>
+  <si>
     <t>PistolShrimp</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="PistolShrimp")</t>
+  </si>
+  <si>
     <t>Pufferfish</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Pufferfish")</t>
+  </si>
+  <si>
     <t>Seasoner</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Seasoner")</t>
+  </si>
+  <si>
     <t>SharkRider</t>
   </si>
   <si>
-    <t>SoundPro</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="SharkRider")</t>
   </si>
   <si>
     <t>Starspawn</t>
   </si>
   <si>
-    <t>TinWoodman</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Starspawn")</t>
   </si>
   <si>
     <t>Ushabti</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Ushabti")</t>
+  </si>
+  <si>
     <t>Wagon</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Wagon")</t>
+  </si>
+  <si>
     <t>Watcher</t>
   </si>
   <si>
-    <t>Weaponmaster</t>
-  </si>
-  <si>
-    <t>Wolfron</t>
-  </si>
-  <si>
-    <t>M_Balrog_Atk</t>
-  </si>
-  <si>
-    <t>M_Bearking_Atk</t>
-  </si>
-  <si>
-    <t>M_BombSpider_Atk</t>
-  </si>
-  <si>
-    <t>M_BronzeGear_Atk</t>
-  </si>
-  <si>
-    <t>M_Cell_Atk</t>
-  </si>
-  <si>
-    <t>M_Cursedmass_Atk</t>
-  </si>
-  <si>
-    <t>M_DieS_Atk</t>
-  </si>
-  <si>
-    <t>M_DoctorMacaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Famine_Atk</t>
-  </si>
-  <si>
-    <t>M_FelicisMachine_Atk</t>
-  </si>
-  <si>
-    <t>M_FelicisShinobi_Atk</t>
-  </si>
-  <si>
-    <t>M_Fiti_Atk</t>
-  </si>
-  <si>
-    <t>M_Gemini_Scythe_Atk</t>
-  </si>
-  <si>
-    <t>M_GhostMacaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Graf_Atk</t>
-  </si>
-  <si>
-    <t>M_GuardianTreant_Atk</t>
-  </si>
-  <si>
-    <t>M_HackingTool_Atk</t>
-  </si>
-  <si>
-    <t>M_Hanged_Macaron_Atk</t>
-  </si>
-  <si>
-    <t>M_HoneyMos_Atk</t>
-  </si>
-  <si>
-    <t>M_Jellyfish_Atk</t>
-  </si>
-  <si>
-    <t>M_Karakasa_Atk</t>
-  </si>
-  <si>
-    <t>M_Kraken_Atk</t>
-  </si>
-  <si>
-    <t>M_KrakenTentacle_Atk</t>
-  </si>
-  <si>
-    <t>M_Leechking_Atk</t>
-  </si>
-  <si>
-    <t>M_LikeStatue_Atk</t>
-  </si>
-  <si>
-    <t>M_LordFelice_Atk</t>
-  </si>
-  <si>
-    <t>M_Makane_Atk</t>
-  </si>
-  <si>
-    <t>M_Mandragora_Atk</t>
-  </si>
-  <si>
-    <t>M_MaskScarecrow_Atk</t>
-  </si>
-  <si>
-    <t>M_Mechanicus_Atk</t>
-  </si>
-  <si>
-    <t>M_Megaron_Atk</t>
-  </si>
-  <si>
-    <t>M_Mimic_Atk</t>
-  </si>
-  <si>
-    <t>M_Octopus_Atk</t>
-  </si>
-  <si>
-    <t>M_PistolShrimp_Atk</t>
-  </si>
-  <si>
-    <t>M_Pufferfish_Atk</t>
-  </si>
-  <si>
-    <t>M_Seasoner_Atk</t>
-  </si>
-  <si>
-    <t>M_SharkRider_Atk</t>
-  </si>
-  <si>
-    <t>M_SoundPro_Atk</t>
-  </si>
-  <si>
-    <t>M_Starspawn_Atk</t>
-  </si>
-  <si>
-    <t>M_TinWoodman_Atk</t>
-  </si>
-  <si>
-    <t>M_Ushabti_Atk</t>
-  </si>
-  <si>
-    <t>M_Wagon_Atk</t>
-  </si>
-  <si>
-    <t>M_Watcher_Atk</t>
-  </si>
-  <si>
-    <t>M_Weaponmaster_Atk</t>
-  </si>
-  <si>
-    <t>M_Wolfron_Atk</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Watcher")</t>
   </si>
 </sst>
 </file>
@@ -1284,11 +1239,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="20.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1345,10 +1297,10 @@
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1374,10 +1326,10 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1386,7 +1338,10 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1412,37 +1367,37 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>600</v>
+        <v>288</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K4">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L4">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M4">
         <v>0.05</v>
@@ -1450,19 +1405,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1480,7 +1435,7 @@
         <v>14</v>
       </c>
       <c r="L5">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M5">
         <v>0.05</v>
@@ -1488,189 +1443,189 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K6">
         <v>14</v>
       </c>
       <c r="L6">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="M6">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>40</v>
       </c>
       <c r="K7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L7">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="M7">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>40</v>
       </c>
       <c r="K8">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L8">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>600</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24</v>
+      </c>
+      <c r="K9">
         <v>30</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>320</v>
-      </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9">
-        <v>14</v>
-      </c>
       <c r="L9">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M9">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>600</v>
+        <v>288</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K10">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L10">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M10">
         <v>0.05</v>
@@ -1678,171 +1633,171 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>288</v>
+        <v>3200</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="L11">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>3200</v>
+        <v>360</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="K12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L12">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="M12">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K13">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L13">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="M13">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K14">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L14">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="M14">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1868,45 +1823,45 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="K16">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <v>450</v>
       </c>
       <c r="M16">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1915,10 +1870,10 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1936,7 +1891,7 @@
         <v>20</v>
       </c>
       <c r="L17">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M17">
         <v>0.1</v>
@@ -1944,7 +1899,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1953,238 +1908,241 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>55</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>400</v>
+        <v>3200</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
         <v>40</v>
       </c>
-      <c r="K18">
-        <v>20</v>
-      </c>
       <c r="L18">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="M18">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3200</v>
+        <v>640</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K19">
-        <v>40</v>
+        <v>16.799999</v>
       </c>
       <c r="L19">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="M19">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>640</v>
+        <v>400</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K20">
-        <v>16.799999</v>
+        <v>20</v>
       </c>
       <c r="L20">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M20">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K21">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <v>550</v>
       </c>
       <c r="M21">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="M22">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>360</v>
+        <v>3200</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L23">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M23">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2202,7 +2160,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M24">
         <v>0.05</v>
@@ -2210,10 +2168,10 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -2222,63 +2180,63 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>3200</v>
+        <v>2560</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L25">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="M25">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>576</v>
+        <v>960</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K26">
-        <v>16.799999</v>
+        <v>25.200001</v>
       </c>
       <c r="L26">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M26">
         <v>0.05</v>
@@ -2286,86 +2244,86 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>3200</v>
+        <v>288</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="K27">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="L27">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M27">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="K28">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L28">
         <v>400</v>
       </c>
       <c r="M28">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -2374,7 +2332,10 @@
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>96</v>
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>80</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2392,7 +2353,7 @@
         <v>28</v>
       </c>
       <c r="L29">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M29">
         <v>0.2</v>
@@ -2400,37 +2361,37 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
+        <v>720</v>
+      </c>
+      <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
+        <v>42</v>
+      </c>
+      <c r="K30">
+        <v>24</v>
+      </c>
+      <c r="L30">
         <v>600</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>24</v>
-      </c>
-      <c r="K30">
-        <v>30</v>
-      </c>
-      <c r="L30">
-        <v>550</v>
       </c>
       <c r="M30">
         <v>0.05</v>
@@ -2438,75 +2399,75 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>960</v>
+        <v>320</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K31">
-        <v>25.200001</v>
+        <v>14</v>
       </c>
       <c r="L31">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="M31">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>600</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <v>24</v>
       </c>
-      <c r="D32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" t="s">
-        <v>99</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>288</v>
-      </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
-      <c r="J32">
-        <v>28</v>
-      </c>
       <c r="K32">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L32">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="M32">
         <v>0.05</v>
@@ -2514,19 +2475,19 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2544,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="L33">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="M33">
         <v>0.15</v>
@@ -2552,113 +2513,113 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>2560</v>
+        <v>288</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="K34">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L34">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M34">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K35">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L35">
         <v>600</v>
       </c>
       <c r="M35">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>320</v>
+        <v>800</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K36">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L36">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="M36">
         <v>0.15</v>
@@ -2666,37 +2627,37 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K37">
-        <v>30</v>
+        <v>25.200001</v>
       </c>
       <c r="L37">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="M37">
         <v>0.05</v>
@@ -2704,37 +2665,37 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>320</v>
+        <v>800</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K38">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L38">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="M38">
         <v>0.15</v>
@@ -2742,381 +2703,39 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K39">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L39">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="M39">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>400</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>40</v>
-      </c>
-      <c r="K40">
-        <v>20</v>
-      </c>
-      <c r="L40">
-        <v>600</v>
-      </c>
-      <c r="M40">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" t="s">
-        <v>108</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>400</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>40</v>
-      </c>
-      <c r="K41">
-        <v>20</v>
-      </c>
-      <c r="L41">
-        <v>500</v>
-      </c>
-      <c r="M41">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" t="s">
-        <v>42</v>
-      </c>
-      <c r="E42" t="s">
-        <v>109</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>800</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>60</v>
-      </c>
-      <c r="K42">
-        <v>24</v>
-      </c>
-      <c r="L42">
-        <v>550</v>
-      </c>
-      <c r="M42">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" t="s">
-        <v>110</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>320</v>
-      </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
-        <v>40</v>
-      </c>
-      <c r="K43">
-        <v>14</v>
-      </c>
-      <c r="L43">
-        <v>500</v>
-      </c>
-      <c r="M43">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" t="s">
-        <v>111</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>960</v>
-      </c>
-      <c r="I44">
-        <v>100</v>
-      </c>
-      <c r="J44">
-        <v>36</v>
-      </c>
-      <c r="K44">
-        <v>25.200001</v>
-      </c>
-      <c r="L44">
-        <v>450</v>
-      </c>
-      <c r="M44">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>800</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>60</v>
-      </c>
-      <c r="K45">
-        <v>24</v>
-      </c>
-      <c r="L45">
-        <v>550</v>
-      </c>
-      <c r="M45">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" t="s">
-        <v>113</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>400</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>40</v>
-      </c>
-      <c r="K46">
-        <v>20</v>
-      </c>
-      <c r="L46">
-        <v>550</v>
-      </c>
-      <c r="M46">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" t="s">
-        <v>114</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>3200</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>100</v>
-      </c>
-      <c r="K47">
-        <v>40</v>
-      </c>
-      <c r="L47">
-        <v>500</v>
-      </c>
-      <c r="M47">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" t="s">
-        <v>115</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>400</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>40</v>
-      </c>
-      <c r="K48">
-        <v>20</v>
-      </c>
-      <c r="L48">
-        <v>450</v>
-      </c>
-      <c r="M48">
         <v>0.1</v>
       </c>
     </row>

--- a/DesignData/Excel_Masters/EnemyStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyStats_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="102">
   <si>
     <t>---</t>
   </si>
@@ -39,6 +39,9 @@
     <t>PatternActionHandles</t>
   </si>
   <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
     <t>SummonCost</t>
   </si>
   <si>
@@ -81,48 +84,48 @@
     <t>Bearking</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Bearking")</t>
+  </si>
+  <si>
+    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat2"))</t>
+  </si>
+  <si>
+    <t>BronzeGear</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Role.Support")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Rank.Normal")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="BronzeGear")</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cell")</t>
+  </si>
+  <si>
+    <t>Cursedmass</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cursedmass")</t>
+  </si>
+  <si>
+    <t>DanceMakane</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="DanceMakane")</t>
+  </si>
+  <si>
+    <t>Deatheye</t>
+  </si>
+  <si>
     <t>(TagName="Unit.Attack.Range")</t>
   </si>
   <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Bearking")</t>
-  </si>
-  <si>
-    <t>((DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat1"),(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyPatternStats.DT_EnemyPatternStats'",RowName="Bearking_Pat2"))</t>
-  </si>
-  <si>
-    <t>BronzeGear</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Role.Support")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Rank.Normal")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="BronzeGear")</t>
-  </si>
-  <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cell")</t>
-  </si>
-  <si>
-    <t>Cursedmass</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Cursedmass")</t>
-  </si>
-  <si>
-    <t>DanceMakane</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="DanceMakane")</t>
-  </si>
-  <si>
-    <t>Deatheye</t>
-  </si>
-  <si>
     <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Deatheye")</t>
   </si>
   <si>
@@ -165,10 +168,10 @@
     <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Fiti")</t>
   </si>
   <si>
-    <t>Gemini_Scythe</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Gemini_Scythe")</t>
+    <t>GeminiScythe</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="GeminiScythe")</t>
   </si>
   <si>
     <t>GhostMacaron</t>
@@ -1239,10 +1242,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1282,60 +1285,63 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>3200</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>40</v>
+      </c>
+      <c r="M2">
+        <v>600</v>
+      </c>
+      <c r="N2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>3200</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
-      </c>
-      <c r="K2">
-        <v>40</v>
-      </c>
-      <c r="L2">
-        <v>600</v>
-      </c>
-      <c r="M2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -1343,34 +1349,34 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>2560</v>
       </c>
-      <c r="I3">
-        <v>100</v>
-      </c>
       <c r="J3">
         <v>100</v>
       </c>
       <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
         <v>28</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>500</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
@@ -1381,34 +1387,34 @@
       <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>288</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
       <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
         <v>28</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>14</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>400</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
@@ -1419,37 +1425,37 @@
       <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>288</v>
       </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
       <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
         <v>28</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>14</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>500</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -1457,37 +1463,37 @@
       <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>320</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>40</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>450</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -1495,110 +1501,110 @@
       <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>400</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>40</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>20</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>400</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>320</v>
       </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
       <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
         <v>40</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>14</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>500</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>600</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>24</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>30</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>600</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
@@ -1607,74 +1613,74 @@
         <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>288</v>
       </c>
-      <c r="I10">
-        <v>100</v>
-      </c>
       <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
         <v>28</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>14</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>500</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>3200</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>3200</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
-      <c r="K11">
-        <v>40</v>
-      </c>
-      <c r="L11">
+      <c r="M11">
         <v>400</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -1683,343 +1689,343 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>360</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
       <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
         <v>28</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>20</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>450</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>320</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
         <v>40</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>14</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>500</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>600</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>24</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>30</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>450</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>600</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>24</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>30</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>450</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>400</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>40</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>20</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>450</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>400</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>40</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>20</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>550</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>3200</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>40</v>
+      </c>
+      <c r="M18">
+        <v>500</v>
+      </c>
+      <c r="N18">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>640</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>60</v>
+      </c>
+      <c r="L19">
+        <v>16.799999</v>
+      </c>
+      <c r="M19">
+        <v>550</v>
+      </c>
+      <c r="N19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C20" t="s">
         <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>3200</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
-      <c r="K18">
-        <v>40</v>
-      </c>
-      <c r="L18">
-        <v>500</v>
-      </c>
-      <c r="M18">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>640</v>
-      </c>
-      <c r="I19">
-        <v>100</v>
-      </c>
-      <c r="J19">
-        <v>60</v>
-      </c>
-      <c r="K19">
-        <v>16.799999</v>
-      </c>
-      <c r="L19">
-        <v>550</v>
-      </c>
-      <c r="M19">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>400</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>40</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>20</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>450</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
@@ -2028,226 +2034,226 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>360</v>
       </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>28</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>20</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>550</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>480</v>
       </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
       <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>24</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>21</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>500</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.05</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>3200</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
       <c r="J23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>40</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>450</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>480</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>24</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>21</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>400</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>2560</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>28</v>
+      </c>
+      <c r="M25">
+        <v>600</v>
+      </c>
+      <c r="N25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>960</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>36</v>
+      </c>
+      <c r="L26">
+        <v>25.200001</v>
+      </c>
+      <c r="M26">
+        <v>550</v>
+      </c>
+      <c r="N26">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" t="s">
         <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>2560</v>
-      </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-      <c r="K25">
-        <v>28</v>
-      </c>
-      <c r="L25">
-        <v>600</v>
-      </c>
-      <c r="M25">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>960</v>
-      </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>36</v>
-      </c>
-      <c r="K26">
-        <v>25.200001</v>
-      </c>
-      <c r="L26">
-        <v>550</v>
-      </c>
-      <c r="M26">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s">
-        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
@@ -2256,267 +2262,267 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>288</v>
       </c>
-      <c r="I27">
-        <v>100</v>
-      </c>
       <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
         <v>28</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>14</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>500</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>320</v>
       </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
       <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
         <v>40</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>14</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>400</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2560</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>28</v>
+      </c>
+      <c r="M29">
+        <v>500</v>
+      </c>
+      <c r="N29">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
         <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>2560</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
-      <c r="K29">
-        <v>28</v>
-      </c>
-      <c r="L29">
-        <v>500</v>
-      </c>
-      <c r="M29">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" t="s">
-        <v>14</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>720</v>
       </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
       <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
         <v>42</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>24</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>600</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
         <v>320</v>
       </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
       <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
         <v>40</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>14</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>400</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.15</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <v>600</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>24</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>30</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>550</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>0.05</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
         <v>320</v>
       </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
       <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
         <v>40</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>14</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>450</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
         <v>24</v>
@@ -2525,217 +2531,217 @@
         <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>288</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
       <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
         <v>28</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>14</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>600</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>0.05</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>400</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
       <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>40</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>20</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>600</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>800</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>60</v>
+      </c>
+      <c r="L36">
+        <v>24</v>
+      </c>
+      <c r="M36">
+        <v>550</v>
+      </c>
+      <c r="N36">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
         <v>15</v>
       </c>
-      <c r="D36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>960</v>
+      </c>
+      <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>36</v>
+      </c>
+      <c r="L37">
+        <v>25.200001</v>
+      </c>
+      <c r="M37">
+        <v>450</v>
+      </c>
+      <c r="N37">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>800</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>60</v>
       </c>
-      <c r="K36">
+      <c r="L38">
         <v>24</v>
       </c>
-      <c r="L36">
+      <c r="M38">
         <v>550</v>
       </c>
-      <c r="M36">
+      <c r="N38">
         <v>0.15</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" t="s">
-        <v>96</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>960</v>
-      </c>
-      <c r="I37">
-        <v>100</v>
-      </c>
-      <c r="J37">
-        <v>36</v>
-      </c>
-      <c r="K37">
-        <v>25.200001</v>
-      </c>
-      <c r="L37">
-        <v>450</v>
-      </c>
-      <c r="M37">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
         <v>15</v>
       </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" t="s">
-        <v>98</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>800</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>60</v>
-      </c>
-      <c r="K38">
-        <v>24</v>
-      </c>
-      <c r="L38">
-        <v>550</v>
-      </c>
-      <c r="M38">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>99</v>
-      </c>
-      <c r="B39" t="s">
-        <v>14</v>
-      </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>400</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
         <v>40</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>20</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>550</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>0.1</v>
       </c>
     </row>

--- a/DesignData/Excel_Masters/EnemyStats_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyStats_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="104">
   <si>
     <t>---</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Watcher")</t>
+  </si>
+  <si>
+    <t>Foxhound</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Enemy/DT_EnemyBasicAttackStats.DT_EnemyBasicAttackStats'",RowName="Foxhound")</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1791,83 +1797,83 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>3000</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>25</v>
       </c>
-      <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>600</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>24</v>
-      </c>
-      <c r="L15">
-        <v>30</v>
-      </c>
       <c r="M15">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="N15">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M16">
         <v>450</v>
       </c>
       <c r="N16">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1879,7 +1885,7 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1897,7 +1903,7 @@
         <v>20</v>
       </c>
       <c r="M17">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="N17">
         <v>0.1</v>
@@ -1905,7 +1911,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
@@ -1914,183 +1920,183 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M18">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="N18">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>640</v>
+        <v>3200</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>16.799999</v>
+        <v>40</v>
       </c>
       <c r="M19">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="N19">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>400</v>
+        <v>640</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L20">
-        <v>20</v>
+        <v>16.799999</v>
       </c>
       <c r="M20">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="N20">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L21">
         <v>20</v>
       </c>
       <c r="M21">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="N21">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M22">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="N22">
         <v>0.05</v>
@@ -2098,189 +2104,189 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>3200</v>
+        <v>480</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="L23">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="M23">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="N23">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>480</v>
+        <v>3200</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="M24">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="N24">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>2560</v>
+        <v>480</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="L25">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M25">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="N25">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>960</v>
+        <v>2560</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>25.200001</v>
+        <v>28</v>
       </c>
       <c r="M26">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="N26">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>288</v>
+        <v>960</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L27">
-        <v>14</v>
+        <v>25.200001</v>
       </c>
       <c r="M27">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="N27">
         <v>0.05</v>
@@ -2288,314 +2294,314 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L28">
         <v>14</v>
       </c>
       <c r="M28">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N28">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>2560</v>
+        <v>320</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L29">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M29">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N29">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="F30" t="s">
+        <v>81</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>720</v>
+        <v>2560</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M30">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N30">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>320</v>
+        <v>720</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L31">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M31">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N31">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>600</v>
+        <v>320</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="M32">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="N32">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="J33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L33">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M33">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="N33">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
         <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="L34">
         <v>14</v>
       </c>
       <c r="M34">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="N34">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L35">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M35">
         <v>600</v>
       </c>
       <c r="N35">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
@@ -2604,148 +2610,189 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L36">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M36">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="N36">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
         <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="L37">
-        <v>25.200001</v>
+        <v>24</v>
       </c>
       <c r="M37">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="N37">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
         <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>800</v>
+        <v>960</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L38">
-        <v>24</v>
+        <v>25.200001</v>
       </c>
       <c r="M38">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="N38">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L39">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M39">
         <v>550</v>
       </c>
       <c r="N39">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>400</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>40</v>
+      </c>
+      <c r="L40">
+        <v>20</v>
+      </c>
+      <c r="M40">
+        <v>550</v>
+      </c>
+      <c r="N40">
         <v>0.1</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:N40">
+    <sortCondition ref="A2"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
